--- a/plantillas/Opiniones_Demarcacion.xlsx
+++ b/plantillas/Opiniones_Demarcacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B50AE80-D257-4880-9092-9CEFB636520A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D696E642-A5CF-4306-BE1F-0F0DA6608B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,8 @@
     <t>Opiniones Nulas SEI: Vía Remota</t>
   </si>
   <si>
-    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS (SICOVACC)</t>
+    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
+SICOVACC 2026</t>
   </si>
 </sst>
 </file>
@@ -135,14 +136,16 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -214,12 +217,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -237,6 +234,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,65 +562,65 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-    </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="5"/>
       <c r="C9" s="1"/>
       <c r="D9"/>
       <c r="E9"/>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="16" t="s">
         <v>2</v>
       </c>
     </row>
@@ -625,7 +628,7 @@
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="11"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>

--- a/plantillas/Opiniones_Demarcacion.xlsx
+++ b/plantillas/Opiniones_Demarcacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D696E642-A5CF-4306-BE1F-0F0DA6608B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B130DF1-2A31-44CE-8353-FBE54D556FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
   </si>
   <si>
     <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
-SICOVACC 2026</t>
+SICOVACC</t>
   </si>
 </sst>
 </file>
@@ -220,6 +220,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -234,12 +240,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,40 +562,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
@@ -610,7 +610,7 @@
       <c r="B8" s="4"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="C9" s="1"/>
       <c r="D9"/>
       <c r="E9"/>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="11" t="s">
         <v>2</v>
       </c>
     </row>
